--- a/docs/vllm_optima_test_plan.xlsx
+++ b/docs/vllm_optima_test_plan.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="231">
   <si>
     <t xml:space="preserve">vLLM Optima - test plan (Tesla T4, vLLM 0.31.0)</t>
   </si>
@@ -709,10 +709,10 @@
     <t xml:space="preserve">Not run yet (new names)</t>
   </si>
   <si>
-    <t xml:space="preserve">Not run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not run in Colab yet. All 29 recordings replayed offline without errors (Oct 11).</t>
+    <t xml:space="preserve">Clicked through in the app on Colab (Oct 15): all 29 recordings listed T01-T29; T01, T08, T19 and T24 played step by step with result cards, settings tables, inference.py and the 4.3x before/after table. No errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(replay of T01-T29)</t>
   </si>
   <si>
     <t xml:space="preserve">Notes: blue text = inputs to type into the app. Test 18: rename lessons.json first, otherwise the lesson from test 17 skips the search. Test 20: run the compiler-crash settings, then the same again with the checkbox on. Tests 21-29: press 'Optimize for this GPU' after the run works.</t>
@@ -1112,7 +1112,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFF4C2"/>
+          <fgColor rgb="FF1D7A5A"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1120,7 +1120,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF1D7A5A"/>
+          <fgColor rgb="FFFFF4C2"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D3" s="5" t="n">
         <f aca="false">COUNTIF(L6:L35,"Pass")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="H3" s="5" t="n">
         <f aca="false">B3-D3-F3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2841,13 +2841,17 @@
         <v>227</v>
       </c>
       <c r="L35" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="N35" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="N35" s="11"/>
-      <c r="O35" s="12"/>
+      <c r="O35" s="12" t="n">
+        <v>46310</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
